--- a/LubanTool/Template/Datas/#localization.xlsx
+++ b/LubanTool/Template/Datas/#localization.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Vn7kMD7eIQao9GHNqRmRwS+lmvYqvPDPUejm0rrURwc="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="cP15wKNOYg+gne2lM90opq0kZLhiUDqcanQXU1tgSYM="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -60,12 +60,24 @@
     <t>繼續</t>
   </si>
   <si>
+    <t>つづきから</t>
+  </si>
+  <si>
+    <t>继续</t>
+  </si>
+  <si>
     <t>Start</t>
   </si>
   <si>
     <t>開始</t>
   </si>
   <si>
+    <t>スタート</t>
+  </si>
+  <si>
+    <t>开始</t>
+  </si>
+  <si>
     <t>Success</t>
   </si>
   <si>
@@ -78,6 +90,21 @@
     <t>太棒了！</t>
   </si>
   <si>
+    <t>すごい！</t>
+  </si>
+  <si>
+    <t>Building</t>
+  </si>
+  <si>
+    <t>施工中...</t>
+  </si>
+  <si>
+    <t>Building...</t>
+  </si>
+  <si>
+    <t>建設中…</t>
+  </si>
+  <si>
     <t>道具</t>
   </si>
   <si>
@@ -109,82 +136,13 @@
   </si>
   <si>
     <t>金币</t>
-  </si>
-  <si>
-    <t>Item_100</t>
-  </si>
-  <si>
-    <t>放大鏡</t>
-  </si>
-  <si>
-    <t>Magnifying glass</t>
-  </si>
-  <si>
-    <t>虫眼鏡</t>
-  </si>
-  <si>
-    <t>放大镜</t>
-  </si>
-  <si>
-    <t>Item_101</t>
-  </si>
-  <si>
-    <t>香煙</t>
-  </si>
-  <si>
-    <t>Cigarettes</t>
-  </si>
-  <si>
-    <t>タバコ</t>
-  </si>
-  <si>
-    <t>香烟</t>
-  </si>
-  <si>
-    <t>Item_102</t>
-  </si>
-  <si>
-    <t>啤酒</t>
-  </si>
-  <si>
-    <t>Beer</t>
-  </si>
-  <si>
-    <t>ビール</t>
-  </si>
-  <si>
-    <t>Item_103</t>
-  </si>
-  <si>
-    <t>手鋸</t>
-  </si>
-  <si>
-    <t>Handsaw</t>
-  </si>
-  <si>
-    <t>手锯</t>
-  </si>
-  <si>
-    <t>Item_104</t>
-  </si>
-  <si>
-    <t>手銬</t>
-  </si>
-  <si>
-    <t>Handcuffs</t>
-  </si>
-  <si>
-    <t>手錠</t>
-  </si>
-  <si>
-    <t>手铐</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -202,22 +160,17 @@
     </font>
     <font>
       <sz val="10.0"/>
-      <color rgb="FF0C0C0C"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <sz val="11.0"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
+      <name val="Microsoft JhengHei"/>
     </font>
   </fonts>
   <fills count="7">
@@ -318,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -328,9 +281,6 @@
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
@@ -340,20 +290,24 @@
     <xf borderId="3" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -587,7 +541,7 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -595,56 +549,57 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="7"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5">
+      <c r="A5" s="8"/>
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
@@ -662,201 +617,351 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="9" t="s">
+      <c r="A6" s="8"/>
+      <c r="B6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>12</v>
       </c>
+      <c r="E6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>14</v>
+      <c r="A7" s="8"/>
+      <c r="B7" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>16</v>
+      <c r="A8" s="8"/>
+      <c r="B8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="10" t="s">
+      <c r="A9" s="8"/>
+      <c r="B9" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8"/>
+      <c r="B10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="B11" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>25</v>
-      </c>
+      <c r="B11" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="B12" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="12" t="s">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9" t="s">
         <v>30</v>
       </c>
+      <c r="C12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="B13" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="12" t="s">
+      <c r="A13" s="8"/>
+      <c r="B13" s="9" t="s">
         <v>35</v>
       </c>
+      <c r="C13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="B14" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>40</v>
-      </c>
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="B15" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>42</v>
-      </c>
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="B16" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>48</v>
-      </c>
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="B17" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+    </row>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
